--- a/Presencas_Nexus.xlsx
+++ b/Presencas_Nexus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_B08F466AA1C933AFB944D9A16B8C2ACC5CEC7706" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21AABFF7-BC36-4D14-BA19-71C35E658BFC}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_B08F466AA1C933AFB944D9A16B8C2ACC5CEC7706" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04D81CB-09B9-4D85-8C90-4704918880B6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3735" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3077,10 +3077,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3541,7 +3537,7 @@
         <v>49</v>
       </c>
       <c r="V2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
         <v>41</v>
@@ -11183,7 +11179,7 @@
         <v>41</v>
       </c>
       <c r="X94" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Y94" t="s">
         <v>41</v>
@@ -13092,7 +13088,7 @@
         <v>41</v>
       </c>
       <c r="X117" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Y117" t="s">
         <v>41</v>
@@ -19379,7 +19375,7 @@
         <v>49</v>
       </c>
       <c r="Q193" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="R193" t="s">
         <v>49</v>
@@ -19477,7 +19473,7 @@
         <v>41</v>
       </c>
       <c r="V194" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="W194" t="s">
         <v>41</v>
@@ -19566,7 +19562,7 @@
         <v>41</v>
       </c>
       <c r="X195" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Y195" t="s">
         <v>41</v>
@@ -20138,7 +20134,7 @@
         <v>41</v>
       </c>
       <c r="U202" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="V202" t="s">
         <v>41</v>
@@ -20713,7 +20709,7 @@
         <v>41</v>
       </c>
       <c r="S209" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="T209" t="s">
         <v>41</v>
@@ -21478,10 +21474,10 @@
         <v>41</v>
       </c>
       <c r="Y218" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Z218" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="AA218" t="s">
         <v>41</v>
@@ -26793,7 +26789,7 @@
         <v>41</v>
       </c>
       <c r="Z282" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="AA282" t="s">
         <v>41</v>
@@ -40759,6 +40755,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
@@ -40767,15 +40772,6 @@
     <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41014,6 +41010,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA71807-42AB-4796-819A-D05E58FD6812}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C571A2A-FB99-4315-8877-923FA1E6D29B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -41024,14 +41028,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA71807-42AB-4796-819A-D05E58FD6812}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48F9669C-CF2C-4EF9-A231-74C317F33261}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48F9669C-CF2C-4EF9-A231-74C317F33261}"/>
 </file>
--- a/Presencas_Nexus.xlsx
+++ b/Presencas_Nexus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_B08F466AA1C933AFB944D9A16B8C2ACC5CEC7706" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04D81CB-09B9-4D85-8C90-4704918880B6}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_B08F466AA1C933AFB944D9A16B8C2ACC5CEC7706" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEDFEE39-5F95-492D-80E5-5F9DD750BA27}"/>
   <bookViews>
-    <workbookView xWindow="3735" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="930" yWindow="2355" windowWidth="21600" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AA$450</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3037,12 +3050,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3057,11 +3076,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3472,7 +3492,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -3555,7 +3575,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -3638,7 +3658,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -3721,7 +3741,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>69</v>
       </c>
@@ -3804,7 +3824,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -3887,7 +3907,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -3970,7 +3990,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>77</v>
       </c>
@@ -4053,7 +4073,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -4136,7 +4156,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -4219,7 +4239,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -4302,7 +4322,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -4385,7 +4405,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>93</v>
       </c>
@@ -4468,7 +4488,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -4551,7 +4571,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -4634,7 +4654,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -4717,7 +4737,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>103</v>
       </c>
@@ -4800,7 +4820,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>105</v>
       </c>
@@ -4883,7 +4903,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>107</v>
       </c>
@@ -4966,7 +4986,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>110</v>
       </c>
@@ -5049,7 +5069,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -5132,7 +5152,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>114</v>
       </c>
@@ -5215,7 +5235,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -5298,7 +5318,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -5381,7 +5401,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -5464,7 +5484,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>122</v>
       </c>
@@ -5547,7 +5567,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -5630,7 +5650,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -5713,7 +5733,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>128</v>
       </c>
@@ -5796,7 +5816,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>130</v>
       </c>
@@ -5879,7 +5899,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -5962,7 +5982,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>134</v>
       </c>
@@ -6045,7 +6065,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>138</v>
       </c>
@@ -6128,7 +6148,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>140</v>
       </c>
@@ -6211,7 +6231,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -6294,7 +6314,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>144</v>
       </c>
@@ -6377,7 +6397,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>146</v>
       </c>
@@ -6460,7 +6480,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>148</v>
       </c>
@@ -6543,7 +6563,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>151</v>
       </c>
@@ -6626,7 +6646,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>154</v>
       </c>
@@ -6709,7 +6729,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -6792,7 +6812,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>158</v>
       </c>
@@ -6875,7 +6895,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>160</v>
       </c>
@@ -6958,7 +6978,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>162</v>
       </c>
@@ -7041,7 +7061,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>165</v>
       </c>
@@ -7124,7 +7144,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>167</v>
       </c>
@@ -7207,7 +7227,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -7290,7 +7310,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>171</v>
       </c>
@@ -7373,7 +7393,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>173</v>
       </c>
@@ -7456,7 +7476,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>175</v>
       </c>
@@ -7539,7 +7559,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>177</v>
       </c>
@@ -7622,7 +7642,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>179</v>
       </c>
@@ -7705,7 +7725,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>181</v>
       </c>
@@ -7788,7 +7808,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>183</v>
       </c>
@@ -7871,7 +7891,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>185</v>
       </c>
@@ -7954,7 +7974,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>187</v>
       </c>
@@ -8037,7 +8057,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>189</v>
       </c>
@@ -8120,7 +8140,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>191</v>
       </c>
@@ -8203,7 +8223,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>193</v>
       </c>
@@ -10859,7 +10879,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>264</v>
       </c>
@@ -10942,7 +10962,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>266</v>
       </c>
@@ -11025,7 +11045,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>268</v>
       </c>
@@ -11274,7 +11294,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>274</v>
       </c>
@@ -11425,7 +11445,7 @@
         <v>41</v>
       </c>
       <c r="W97" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="X97" t="s">
         <v>41</v>
@@ -11523,7 +11543,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>281</v>
       </c>
@@ -11772,7 +11792,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>287</v>
       </c>
@@ -12021,7 +12041,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>293</v>
       </c>
@@ -12353,7 +12373,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>301</v>
       </c>
@@ -12685,7 +12705,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>309</v>
       </c>
@@ -12768,7 +12788,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>311</v>
       </c>
@@ -17416,7 +17436,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>195</v>
       </c>
@@ -17499,7 +17519,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>200</v>
       </c>
@@ -17570,7 +17590,7 @@
         <v>49</v>
       </c>
       <c r="X171" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="Y171" t="s">
         <v>41</v>
@@ -17582,7 +17602,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>202</v>
       </c>
@@ -17652,7 +17672,7 @@
       <c r="W172" t="s">
         <v>41</v>
       </c>
-      <c r="X172" t="s">
+      <c r="X172" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y172" t="s">
@@ -17665,7 +17685,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>204</v>
       </c>
@@ -17748,7 +17768,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>206</v>
       </c>
@@ -17831,7 +17851,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>208</v>
       </c>
@@ -17914,7 +17934,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>210</v>
       </c>
@@ -17997,7 +18017,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>212</v>
       </c>
@@ -18080,7 +18100,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>214</v>
       </c>
@@ -18163,7 +18183,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>216</v>
       </c>
@@ -18236,8 +18256,8 @@
       <c r="X179" t="s">
         <v>41</v>
       </c>
-      <c r="Y179" t="s">
-        <v>49</v>
+      <c r="Y179" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="Z179" t="s">
         <v>41</v>
@@ -18246,7 +18266,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>218</v>
       </c>
@@ -18329,7 +18349,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>221</v>
       </c>
@@ -18412,7 +18432,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>223</v>
       </c>
@@ -18495,7 +18515,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>225</v>
       </c>
@@ -18578,7 +18598,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>227</v>
       </c>
@@ -18661,7 +18681,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>230</v>
       </c>
@@ -18744,7 +18764,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>232</v>
       </c>
@@ -18827,7 +18847,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>234</v>
       </c>
@@ -18910,7 +18930,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>236</v>
       </c>
@@ -18993,7 +19013,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>238</v>
       </c>
@@ -19076,7 +19096,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>240</v>
       </c>
@@ -19132,7 +19152,7 @@
         <v>41</v>
       </c>
       <c r="S190" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="T190" t="s">
         <v>41</v>
@@ -19159,7 +19179,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>242</v>
       </c>
@@ -19242,7 +19262,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>244</v>
       </c>
@@ -19325,7 +19345,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>938</v>
       </c>
@@ -19408,7 +19428,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>941</v>
       </c>
@@ -19491,7 +19511,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>943</v>
       </c>
@@ -19574,7 +19594,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>945</v>
       </c>
@@ -19657,7 +19677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>947</v>
       </c>
@@ -19740,7 +19760,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>949</v>
       </c>
@@ -19823,7 +19843,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>951</v>
       </c>
@@ -19906,7 +19926,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>953</v>
       </c>
@@ -19989,7 +20009,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>955</v>
       </c>
@@ -20072,7 +20092,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>957</v>
       </c>
@@ -20155,7 +20175,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>959</v>
       </c>
@@ -20238,7 +20258,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>961</v>
       </c>
@@ -20321,7 +20341,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>963</v>
       </c>
@@ -20404,7 +20424,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>965</v>
       </c>
@@ -20487,7 +20507,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>967</v>
       </c>
@@ -20570,7 +20590,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>969</v>
       </c>
@@ -20653,7 +20673,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>971</v>
       </c>
@@ -20736,7 +20756,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>973</v>
       </c>
@@ -20819,7 +20839,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>975</v>
       </c>
@@ -20902,7 +20922,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>977</v>
       </c>
@@ -20985,7 +21005,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>979</v>
       </c>
@@ -21068,7 +21088,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>981</v>
       </c>
@@ -21151,7 +21171,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>983</v>
       </c>
@@ -21234,7 +21254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>985</v>
       </c>
@@ -21317,7 +21337,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>987</v>
       </c>
@@ -21400,7 +21420,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>989</v>
       </c>
@@ -21483,7 +21503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>991</v>
       </c>
@@ -21566,7 +21586,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>993</v>
       </c>
@@ -21649,7 +21669,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>995</v>
       </c>
@@ -21732,7 +21752,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>421</v>
       </c>
@@ -21815,7 +21835,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>424</v>
       </c>
@@ -21898,7 +21918,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>426</v>
       </c>
@@ -21981,7 +22001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>428</v>
       </c>
@@ -22064,7 +22084,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>430</v>
       </c>
@@ -22147,7 +22167,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>432</v>
       </c>
@@ -22230,7 +22250,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>434</v>
       </c>
@@ -22313,7 +22333,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>436</v>
       </c>
@@ -22396,7 +22416,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>438</v>
       </c>
@@ -22479,7 +22499,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>440</v>
       </c>
@@ -22562,7 +22582,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>442</v>
       </c>
@@ -22645,7 +22665,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>444</v>
       </c>
@@ -22728,7 +22748,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>446</v>
       </c>
@@ -22811,7 +22831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>448</v>
       </c>
@@ -22894,7 +22914,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>450</v>
       </c>
@@ -22977,7 +22997,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>452</v>
       </c>
@@ -23060,7 +23080,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>454</v>
       </c>
@@ -23143,7 +23163,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>456</v>
       </c>
@@ -23226,7 +23246,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>458</v>
       </c>
@@ -23309,7 +23329,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>460</v>
       </c>
@@ -23392,7 +23412,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>462</v>
       </c>
@@ -23475,7 +23495,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>464</v>
       </c>
@@ -23558,7 +23578,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>466</v>
       </c>
@@ -23641,7 +23661,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>468</v>
       </c>
@@ -23724,7 +23744,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>470</v>
       </c>
@@ -23807,7 +23827,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>472</v>
       </c>
@@ -23890,7 +23910,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>474</v>
       </c>
@@ -23973,7 +23993,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>476</v>
       </c>
@@ -24056,7 +24076,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>478</v>
       </c>
@@ -24139,7 +24159,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>480</v>
       </c>
@@ -24222,7 +24242,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>482</v>
       </c>
@@ -24305,7 +24325,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>484</v>
       </c>
@@ -24388,7 +24408,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>486</v>
       </c>
@@ -24471,7 +24491,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>856</v>
       </c>
@@ -24554,7 +24574,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>860</v>
       </c>
@@ -24637,7 +24657,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>862</v>
       </c>
@@ -24720,7 +24740,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>864</v>
       </c>
@@ -24803,7 +24823,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>866</v>
       </c>
@@ -24886,7 +24906,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>868</v>
       </c>
@@ -24969,7 +24989,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>870</v>
       </c>
@@ -25052,7 +25072,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>872</v>
       </c>
@@ -25135,7 +25155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>874</v>
       </c>
@@ -25218,7 +25238,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>876</v>
       </c>
@@ -25301,7 +25321,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>878</v>
       </c>
@@ -25384,7 +25404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>880</v>
       </c>
@@ -25467,7 +25487,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>882</v>
       </c>
@@ -25550,7 +25570,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>884</v>
       </c>
@@ -25633,7 +25653,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>886</v>
       </c>
@@ -25716,7 +25736,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>888</v>
       </c>
@@ -25799,7 +25819,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>890</v>
       </c>
@@ -25882,7 +25902,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>892</v>
       </c>
@@ -25965,7 +25985,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>894</v>
       </c>
@@ -26048,7 +26068,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>896</v>
       </c>
@@ -26131,7 +26151,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>898</v>
       </c>
@@ -26214,7 +26234,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>900</v>
       </c>
@@ -26297,7 +26317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>902</v>
       </c>
@@ -26380,7 +26400,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>904</v>
       </c>
@@ -26463,7 +26483,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>906</v>
       </c>
@@ -26546,7 +26566,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>908</v>
       </c>
@@ -26629,7 +26649,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>910</v>
       </c>
@@ -26712,7 +26732,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>912</v>
       </c>
@@ -26795,7 +26815,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>914</v>
       </c>
@@ -26878,7 +26898,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>916</v>
       </c>
@@ -26961,7 +26981,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>918</v>
       </c>
@@ -27044,7 +27064,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>920</v>
       </c>
@@ -27127,7 +27147,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>922</v>
       </c>
@@ -27210,7 +27230,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>924</v>
       </c>
@@ -27293,7 +27313,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>926</v>
       </c>
@@ -27376,7 +27396,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>928</v>
       </c>
@@ -27459,7 +27479,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>930</v>
       </c>
@@ -27542,7 +27562,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>932</v>
       </c>
@@ -27625,7 +27645,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>934</v>
       </c>
@@ -27708,7 +27728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>936</v>
       </c>
@@ -37502,7 +37522,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="412" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>27</v>
       </c>
@@ -37585,7 +37605,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="413" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>42</v>
       </c>
@@ -37668,7 +37688,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="414" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>50</v>
       </c>
@@ -37751,7 +37771,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="415" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>784</v>
       </c>
@@ -37834,7 +37854,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="416" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>786</v>
       </c>
@@ -37917,7 +37937,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="417" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>788</v>
       </c>
@@ -38000,7 +38020,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="418" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>790</v>
       </c>
@@ -38083,7 +38103,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="419" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>792</v>
       </c>
@@ -38166,7 +38186,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="420" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>794</v>
       </c>
@@ -38249,7 +38269,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="421" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>796</v>
       </c>
@@ -38332,7 +38352,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="422" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>798</v>
       </c>
@@ -38415,7 +38435,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="423" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>800</v>
       </c>
@@ -38498,7 +38518,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="424" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>802</v>
       </c>
@@ -38581,7 +38601,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="425" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>804</v>
       </c>
@@ -38664,7 +38684,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="426" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>806</v>
       </c>
@@ -38747,7 +38767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="427" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>808</v>
       </c>
@@ -38830,7 +38850,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="428" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>810</v>
       </c>
@@ -38913,7 +38933,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="429" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>812</v>
       </c>
@@ -38996,7 +39016,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="430" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>814</v>
       </c>
@@ -39079,7 +39099,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="431" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>816</v>
       </c>
@@ -39162,7 +39182,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="432" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>818</v>
       </c>
@@ -39245,7 +39265,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="433" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>820</v>
       </c>
@@ -39328,7 +39348,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="434" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>822</v>
       </c>
@@ -39411,7 +39431,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="435" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>824</v>
       </c>
@@ -39494,7 +39514,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="436" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>826</v>
       </c>
@@ -39577,7 +39597,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="437" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>828</v>
       </c>
@@ -39660,7 +39680,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="438" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>830</v>
       </c>
@@ -39743,7 +39763,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="439" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>832</v>
       </c>
@@ -39826,7 +39846,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="440" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>834</v>
       </c>
@@ -39909,7 +39929,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="441" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>836</v>
       </c>
@@ -39992,7 +40012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="442" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>838</v>
       </c>
@@ -40075,7 +40095,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="443" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>840</v>
       </c>
@@ -40158,7 +40178,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="444" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>842</v>
       </c>
@@ -40241,7 +40261,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="445" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>844</v>
       </c>
@@ -40324,7 +40344,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="446" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>846</v>
       </c>
@@ -40407,7 +40427,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="447" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>848</v>
       </c>
@@ -40490,7 +40510,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="448" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>850</v>
       </c>
@@ -40573,7 +40593,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="449" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>852</v>
       </c>
@@ -40656,7 +40676,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="450" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>854</v>
       </c>
@@ -40744,6 +40764,16 @@
     <filterColumn colId="3">
       <filters>
         <filter val="Nacala Porto"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="MOCONE"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="22">
+      <filters>
+        <filter val="Presente"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -40764,17 +40794,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -41009,6 +41028,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA71807-42AB-4796-819A-D05E58FD6812}">
   <ds:schemaRefs>
@@ -41018,17 +41048,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C571A2A-FB99-4315-8877-923FA1E6D29B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48F9669C-CF2C-4EF9-A231-74C317F33261}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41045,4 +41064,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C571A2A-FB99-4315-8877-923FA1E6D29B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Presencas_Nexus.xlsx
+++ b/Presencas_Nexus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_B08F466AA1C933AFB944D9A16B8C2ACC5CEC7706" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEDFEE39-5F95-492D-80E5-5F9DD750BA27}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_B08F466AA1C933AFB944D9A16B8C2ACC5CEC7706" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CCBB212-0B3F-4ABD-B0CC-B09341AFCD6B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="930" yWindow="2355" windowWidth="21600" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3391,16 +3391,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="6" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.28515625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="9.7109375" hidden="1" customWidth="1"/>
@@ -3492,7 +3492,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>103</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>105</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>107</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>110</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>122</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>128</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>130</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>134</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>140</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>144</v>
       </c>
@@ -6397,7 +6397,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>146</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>148</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>151</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>154</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>160</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>167</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>171</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>173</v>
       </c>
@@ -7725,7 +7725,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>181</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>183</v>
       </c>
@@ -7891,7 +7891,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>185</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>193</v>
       </c>
@@ -8306,7 +8306,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>396</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>399</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>401</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>403</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>405</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>407</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>409</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>411</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="68" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>413</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>415</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="70" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>417</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>419</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>558</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="73" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>560</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="74" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>562</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>564</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>566</v>
       </c>
@@ -9717,7 +9717,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="77" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>568</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="78" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>570</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="79" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>572</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="80" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>574</v>
       </c>
@@ -10049,7 +10049,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="81" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>576</v>
       </c>
@@ -10132,7 +10132,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="82" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>578</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="83" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>580</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="84" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>582</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>584</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="86" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>586</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="87" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>588</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="88" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>590</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="89" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>592</v>
       </c>
@@ -13120,7 +13120,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>246</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>252</v>
       </c>
@@ -13286,7 +13286,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="120" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>254</v>
       </c>
@@ -13369,7 +13369,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="121" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>256</v>
       </c>
@@ -13452,7 +13452,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="122" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>258</v>
       </c>
@@ -13535,7 +13535,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="123" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>594</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>596</v>
       </c>
@@ -13701,7 +13701,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="125" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>598</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="126" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>600</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="127" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>602</v>
       </c>
@@ -13950,7 +13950,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>604</v>
       </c>
@@ -14033,7 +14033,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>606</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="130" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>608</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="131" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>610</v>
       </c>
@@ -14282,7 +14282,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="132" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>612</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="133" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>614</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="134" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>616</v>
       </c>
@@ -14531,7 +14531,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="135" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>618</v>
       </c>
@@ -14614,7 +14614,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="136" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>620</v>
       </c>
@@ -14697,7 +14697,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="137" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>622</v>
       </c>
@@ -14780,7 +14780,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="138" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>624</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="139" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>626</v>
       </c>
@@ -14946,7 +14946,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>628</v>
       </c>
@@ -15029,7 +15029,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="141" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>630</v>
       </c>
@@ -15112,7 +15112,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="142" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>632</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="143" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>634</v>
       </c>
@@ -15610,7 +15610,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="148" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>353</v>
       </c>
@@ -15776,7 +15776,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="150" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>357</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="151" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>360</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="152" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>362</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="153" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>488</v>
       </c>
@@ -16108,7 +16108,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="154" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>490</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="155" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>492</v>
       </c>
@@ -16274,7 +16274,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="156" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>494</v>
       </c>
@@ -16357,7 +16357,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="157" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>496</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="158" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>498</v>
       </c>
@@ -16689,7 +16689,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="161" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>504</v>
       </c>
@@ -16772,7 +16772,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="162" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>506</v>
       </c>
@@ -16855,7 +16855,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="163" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>508</v>
       </c>
@@ -16938,7 +16938,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="164" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>510</v>
       </c>
@@ -17021,7 +17021,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="165" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>512</v>
       </c>
@@ -17104,7 +17104,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="166" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>514</v>
       </c>
@@ -17187,7 +17187,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="167" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>516</v>
       </c>
@@ -17270,7 +17270,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="168" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>518</v>
       </c>
@@ -17353,7 +17353,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="169" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>520</v>
       </c>
@@ -17602,7 +17602,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="172" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>202</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="173" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>204</v>
       </c>
@@ -17934,7 +17934,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="176" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>210</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>212</v>
       </c>
@@ -18100,7 +18100,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="178" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>214</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>216</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="181" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>221</v>
       </c>
@@ -18432,7 +18432,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="182" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>223</v>
       </c>
@@ -18515,7 +18515,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="183" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>225</v>
       </c>
@@ -18764,7 +18764,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="186" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>232</v>
       </c>
@@ -18847,7 +18847,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="187" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>234</v>
       </c>
@@ -19096,7 +19096,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="190" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>240</v>
       </c>
@@ -19179,7 +19179,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="191" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>242</v>
       </c>
@@ -19262,7 +19262,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="192" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>244</v>
       </c>
@@ -19428,7 +19428,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="194" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>941</v>
       </c>
@@ -19511,7 +19511,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="195" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>943</v>
       </c>
@@ -19594,7 +19594,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="196" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>945</v>
       </c>
@@ -19677,7 +19677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="197" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>947</v>
       </c>
@@ -19760,7 +19760,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="198" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>949</v>
       </c>
@@ -19843,7 +19843,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="199" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>951</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="200" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>953</v>
       </c>
@@ -20009,7 +20009,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="201" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>955</v>
       </c>
@@ -20092,7 +20092,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="202" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>957</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="203" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>959</v>
       </c>
@@ -20258,7 +20258,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="204" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>961</v>
       </c>
@@ -20341,7 +20341,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="205" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>963</v>
       </c>
@@ -20424,7 +20424,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="206" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>965</v>
       </c>
@@ -20507,7 +20507,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="207" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>967</v>
       </c>
@@ -20590,7 +20590,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="208" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>969</v>
       </c>
@@ -20673,7 +20673,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="209" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>971</v>
       </c>
@@ -20756,7 +20756,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="210" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>973</v>
       </c>
@@ -20839,7 +20839,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="211" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>975</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="212" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>977</v>
       </c>
@@ -21005,7 +21005,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="213" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>979</v>
       </c>
@@ -21088,7 +21088,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="214" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>981</v>
       </c>
@@ -21171,7 +21171,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="215" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>983</v>
       </c>
@@ -21254,7 +21254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="216" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>985</v>
       </c>
@@ -21420,7 +21420,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="218" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>989</v>
       </c>
@@ -21503,7 +21503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="219" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>991</v>
       </c>
@@ -21586,7 +21586,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="220" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>993</v>
       </c>
@@ -21669,7 +21669,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>995</v>
       </c>
@@ -21752,7 +21752,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="222" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>421</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="224" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>426</v>
       </c>
@@ -22001,7 +22001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="225" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>428</v>
       </c>
@@ -22084,7 +22084,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="226" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>430</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="227" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>432</v>
       </c>
@@ -22250,7 +22250,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="228" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>434</v>
       </c>
@@ -22333,7 +22333,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="229" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>436</v>
       </c>
@@ -22582,7 +22582,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="232" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>442</v>
       </c>
@@ -22665,7 +22665,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="233" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>444</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="235" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>448</v>
       </c>
@@ -22997,7 +22997,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="237" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>452</v>
       </c>
@@ -23080,7 +23080,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="238" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>454</v>
       </c>
@@ -23163,7 +23163,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="239" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>456</v>
       </c>
@@ -23246,7 +23246,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="240" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>458</v>
       </c>
@@ -23329,7 +23329,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="241" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>460</v>
       </c>
@@ -23412,7 +23412,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="242" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>462</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="243" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>464</v>
       </c>
@@ -23578,7 +23578,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="244" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>466</v>
       </c>
@@ -23661,7 +23661,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="245" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>468</v>
       </c>
@@ -23910,7 +23910,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="248" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>474</v>
       </c>
@@ -23993,7 +23993,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="249" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>476</v>
       </c>
@@ -24076,7 +24076,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="250" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>478</v>
       </c>
@@ -24242,7 +24242,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="252" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>482</v>
       </c>
@@ -24325,7 +24325,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>484</v>
       </c>
@@ -24408,7 +24408,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="254" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>486</v>
       </c>
@@ -24491,7 +24491,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="255" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>856</v>
       </c>
@@ -24574,7 +24574,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="256" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>860</v>
       </c>
@@ -24740,7 +24740,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="258" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>864</v>
       </c>
@@ -24906,7 +24906,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="260" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>868</v>
       </c>
@@ -24989,7 +24989,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="261" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>870</v>
       </c>
@@ -25072,7 +25072,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="262" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>872</v>
       </c>
@@ -25155,7 +25155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="263" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>874</v>
       </c>
@@ -25321,7 +25321,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="265" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>878</v>
       </c>
@@ -25404,7 +25404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="266" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>880</v>
       </c>
@@ -25487,7 +25487,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="267" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>882</v>
       </c>
@@ -25570,7 +25570,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="268" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>884</v>
       </c>
@@ -25653,7 +25653,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="269" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>886</v>
       </c>
@@ -25736,7 +25736,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="270" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>888</v>
       </c>
@@ -25819,7 +25819,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="271" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>890</v>
       </c>
@@ -25902,7 +25902,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="272" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>892</v>
       </c>
@@ -25985,7 +25985,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="273" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>894</v>
       </c>
@@ -26068,7 +26068,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="274" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>896</v>
       </c>
@@ -26151,7 +26151,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="275" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>898</v>
       </c>
@@ -26234,7 +26234,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="276" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>900</v>
       </c>
@@ -26317,7 +26317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="277" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>902</v>
       </c>
@@ -26400,7 +26400,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="278" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>904</v>
       </c>
@@ -26483,7 +26483,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="279" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>906</v>
       </c>
@@ -26732,7 +26732,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="282" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>912</v>
       </c>
@@ -26981,7 +26981,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="285" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>918</v>
       </c>
@@ -27064,7 +27064,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="286" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>920</v>
       </c>
@@ -27147,7 +27147,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="287" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>922</v>
       </c>
@@ -27230,7 +27230,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="288" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>924</v>
       </c>
@@ -27313,7 +27313,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="289" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>926</v>
       </c>
@@ -27396,7 +27396,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="290" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>928</v>
       </c>
@@ -27479,7 +27479,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="291" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>930</v>
       </c>
@@ -27562,7 +27562,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="292" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>932</v>
       </c>
@@ -27728,7 +27728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="294" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>936</v>
       </c>
@@ -27811,7 +27811,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="295" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>130</v>
       </c>
@@ -27894,7 +27894,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="296" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>376</v>
       </c>
@@ -27977,7 +27977,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="297" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>378</v>
       </c>
@@ -28060,7 +28060,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="298" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>380</v>
       </c>
@@ -28143,7 +28143,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="299" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>382</v>
       </c>
@@ -28226,7 +28226,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="300" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>384</v>
       </c>
@@ -28309,7 +28309,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="301" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>386</v>
       </c>
@@ -28392,7 +28392,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="302" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>388</v>
       </c>
@@ -28475,7 +28475,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="303" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>390</v>
       </c>
@@ -28558,7 +28558,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="304" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>392</v>
       </c>
@@ -28641,7 +28641,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="305" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>394</v>
       </c>
@@ -28807,7 +28807,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="307" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>524</v>
       </c>
@@ -29139,7 +29139,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="311" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>532</v>
       </c>
@@ -29222,7 +29222,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="312" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>534</v>
       </c>
@@ -29305,7 +29305,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="313" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>536</v>
       </c>
@@ -29388,7 +29388,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="314" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>538</v>
       </c>
@@ -29471,7 +29471,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="315" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>540</v>
       </c>
@@ -29554,7 +29554,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="316" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>542</v>
       </c>
@@ -29637,7 +29637,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="317" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>544</v>
       </c>
@@ -29720,7 +29720,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="318" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>546</v>
       </c>
@@ -29886,7 +29886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="320" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>550</v>
       </c>
@@ -29969,7 +29969,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="321" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>552</v>
       </c>
@@ -30052,7 +30052,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="322" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>554</v>
       </c>
@@ -30135,7 +30135,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="323" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>556</v>
       </c>
@@ -30218,7 +30218,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="324" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>364</v>
       </c>
@@ -30301,7 +30301,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="325" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>367</v>
       </c>
@@ -30384,7 +30384,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="326" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>369</v>
       </c>
@@ -30467,7 +30467,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="327" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>371</v>
       </c>
@@ -30550,7 +30550,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="328" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>642</v>
       </c>
@@ -30633,7 +30633,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="329" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>644</v>
       </c>
@@ -30716,7 +30716,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="330" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>646</v>
       </c>
@@ -30799,7 +30799,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="331" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>648</v>
       </c>
@@ -30882,7 +30882,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="332" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>650</v>
       </c>
@@ -30965,7 +30965,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="333" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>652</v>
       </c>
@@ -31131,7 +31131,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="335" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>656</v>
       </c>
@@ -31214,7 +31214,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="336" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>658</v>
       </c>
@@ -31297,7 +31297,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="337" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>660</v>
       </c>
@@ -31380,7 +31380,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="338" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>662</v>
       </c>
@@ -31463,7 +31463,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="339" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>664</v>
       </c>
@@ -31546,7 +31546,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="340" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>666</v>
       </c>
@@ -31629,7 +31629,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="341" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>668</v>
       </c>
@@ -31712,7 +31712,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="342" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>670</v>
       </c>
@@ -31878,7 +31878,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="344" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>674</v>
       </c>
@@ -31961,7 +31961,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="345" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>676</v>
       </c>
@@ -32044,7 +32044,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="346" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>678</v>
       </c>
@@ -32127,7 +32127,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="347" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>680</v>
       </c>
@@ -32210,7 +32210,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="348" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>682</v>
       </c>
@@ -32293,7 +32293,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="349" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>684</v>
       </c>
@@ -32376,7 +32376,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="350" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>686</v>
       </c>
@@ -32459,7 +32459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="351" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>688</v>
       </c>
@@ -32542,7 +32542,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="352" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>690</v>
       </c>
@@ -32625,7 +32625,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="353" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>692</v>
       </c>
@@ -32791,7 +32791,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="355" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>324</v>
       </c>
@@ -32874,7 +32874,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="356" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>326</v>
       </c>
@@ -33040,7 +33040,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="358" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>330</v>
       </c>
@@ -33123,7 +33123,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="359" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>332</v>
       </c>
@@ -33206,7 +33206,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="360" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>334</v>
       </c>
@@ -33289,7 +33289,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="361" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>336</v>
       </c>
@@ -33372,7 +33372,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="362" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>338</v>
       </c>
@@ -33455,7 +33455,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="363" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>340</v>
       </c>
@@ -33538,7 +33538,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="364" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>342</v>
       </c>
@@ -33621,7 +33621,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="365" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>344</v>
       </c>
@@ -33704,7 +33704,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="366" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>346</v>
       </c>
@@ -33787,7 +33787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="367" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>694</v>
       </c>
@@ -33870,7 +33870,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="368" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>696</v>
       </c>
@@ -33953,7 +33953,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="369" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>698</v>
       </c>
@@ -34036,7 +34036,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="370" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>700</v>
       </c>
@@ -34119,7 +34119,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="371" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>702</v>
       </c>
@@ -34202,7 +34202,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="372" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>704</v>
       </c>
@@ -34285,7 +34285,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="373" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>706</v>
       </c>
@@ -34368,7 +34368,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="374" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>708</v>
       </c>
@@ -34451,7 +34451,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="375" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>710</v>
       </c>
@@ -34534,7 +34534,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="376" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>712</v>
       </c>
@@ -34617,7 +34617,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="377" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>714</v>
       </c>
@@ -34700,7 +34700,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="378" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>716</v>
       </c>
@@ -34783,7 +34783,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="379" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>718</v>
       </c>
@@ -34949,7 +34949,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="381" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>722</v>
       </c>
@@ -35032,7 +35032,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="382" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>724</v>
       </c>
@@ -35115,7 +35115,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="383" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>726</v>
       </c>
@@ -35281,7 +35281,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="385" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>730</v>
       </c>
@@ -35364,7 +35364,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="386" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>732</v>
       </c>
@@ -35447,7 +35447,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="387" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>734</v>
       </c>
@@ -35530,7 +35530,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="388" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>736</v>
       </c>
@@ -35613,7 +35613,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="389" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>738</v>
       </c>
@@ -35696,7 +35696,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="390" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>740</v>
       </c>
@@ -35779,7 +35779,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="391" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>742</v>
       </c>
@@ -35862,7 +35862,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="392" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>744</v>
       </c>
@@ -35945,7 +35945,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="393" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>746</v>
       </c>
@@ -36028,7 +36028,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="394" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>748</v>
       </c>
@@ -36111,7 +36111,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="395" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>750</v>
       </c>
@@ -36194,7 +36194,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="396" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>752</v>
       </c>
@@ -36277,7 +36277,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="397" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>754</v>
       </c>
@@ -36360,7 +36360,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="398" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>756</v>
       </c>
@@ -36526,7 +36526,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="400" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>760</v>
       </c>
@@ -36692,7 +36692,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="402" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>764</v>
       </c>
@@ -36858,7 +36858,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="404" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>768</v>
       </c>
@@ -36941,7 +36941,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="405" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>770</v>
       </c>
@@ -37024,7 +37024,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="406" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>772</v>
       </c>
@@ -37107,7 +37107,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="407" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>774</v>
       </c>
@@ -37190,7 +37190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="408" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>776</v>
       </c>
@@ -37439,7 +37439,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="411" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>782</v>
       </c>
@@ -37522,7 +37522,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="412" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>27</v>
       </c>
@@ -37605,7 +37605,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="413" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>42</v>
       </c>
@@ -37688,7 +37688,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="414" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>50</v>
       </c>
@@ -37771,7 +37771,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="415" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>784</v>
       </c>
@@ -37854,7 +37854,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="416" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>786</v>
       </c>
@@ -37937,7 +37937,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="417" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>788</v>
       </c>
@@ -38020,7 +38020,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="418" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>790</v>
       </c>
@@ -38103,7 +38103,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="419" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>792</v>
       </c>
@@ -38186,7 +38186,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="420" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>794</v>
       </c>
@@ -38269,7 +38269,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="421" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>796</v>
       </c>
@@ -38352,7 +38352,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="422" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>798</v>
       </c>
@@ -38435,7 +38435,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="423" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>800</v>
       </c>
@@ -38518,7 +38518,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="424" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>802</v>
       </c>
@@ -38601,7 +38601,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="425" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>804</v>
       </c>
@@ -38684,7 +38684,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="426" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>806</v>
       </c>
@@ -38767,7 +38767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="427" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>808</v>
       </c>
@@ -38850,7 +38850,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="428" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>810</v>
       </c>
@@ -38933,7 +38933,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="429" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>812</v>
       </c>
@@ -39016,7 +39016,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="430" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>814</v>
       </c>
@@ -39099,7 +39099,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="431" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>816</v>
       </c>
@@ -39265,7 +39265,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="433" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>820</v>
       </c>
@@ -39348,7 +39348,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="434" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>822</v>
       </c>
@@ -39431,7 +39431,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="435" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>824</v>
       </c>
@@ -39514,7 +39514,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="436" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>826</v>
       </c>
@@ -39680,7 +39680,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="438" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>830</v>
       </c>
@@ -39763,7 +39763,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="439" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>832</v>
       </c>
@@ -39846,7 +39846,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="440" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>834</v>
       </c>
@@ -39929,7 +39929,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="441" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>836</v>
       </c>
@@ -40012,7 +40012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="442" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>838</v>
       </c>
@@ -40095,7 +40095,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="443" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>840</v>
       </c>
@@ -40178,7 +40178,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="444" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>842</v>
       </c>
@@ -40261,7 +40261,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="445" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>844</v>
       </c>
@@ -40427,7 +40427,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="447" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>848</v>
       </c>
@@ -40510,7 +40510,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="448" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>850</v>
       </c>
@@ -40676,7 +40676,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="450" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>854</v>
       </c>
@@ -40761,16 +40761,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AA450" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Nacala Porto"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters>
-        <filter val="MOCONE"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="22">
       <filters>
         <filter val="Presente"/>
@@ -40781,6 +40771,7 @@
     <sortCondition ref="I1:I450"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -40794,6 +40785,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -41028,17 +41030,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA71807-42AB-4796-819A-D05E58FD6812}">
   <ds:schemaRefs>
@@ -41048,6 +41039,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C571A2A-FB99-4315-8877-923FA1E6D29B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48F9669C-CF2C-4EF9-A231-74C317F33261}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41064,15 +41066,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C571A2A-FB99-4315-8877-923FA1E6D29B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>